--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV_Fiets.xlsx
@@ -388,7 +388,7 @@
         <v>0.4238064353770303</v>
       </c>
       <c r="C2">
-        <v>0.5914781857011085</v>
+        <v>0.5914781857011084</v>
       </c>
       <c r="D2">
         <v>0.6827356175898305</v>
@@ -439,7 +439,7 @@
         <v>0.4857654653692099</v>
       </c>
       <c r="C5">
-        <v>0.6639177403196133</v>
+        <v>0.6639177403196131</v>
       </c>
       <c r="D5">
         <v>0.7328281215101273</v>
@@ -456,7 +456,7 @@
         <v>0.4764492964914863</v>
       </c>
       <c r="C6">
-        <v>0.6526352638223126</v>
+        <v>0.6526352638223125</v>
       </c>
       <c r="D6">
         <v>0.7222865935179038</v>
@@ -473,7 +473,7 @@
         <v>0.5000459747052058</v>
       </c>
       <c r="C7">
-        <v>0.6794437767110588</v>
+        <v>0.6794437767110587</v>
       </c>
       <c r="D7">
         <v>0.7533715401581433</v>
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.4343970284190022</v>
+        <v>0.4343970284190021</v>
       </c>
       <c r="C8">
         <v>0.6051242423863379</v>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.4238064353770303</v>
+        <v>1.432059709480588</v>
       </c>
       <c r="C2">
-        <v>0.5914781857011084</v>
+        <v>0.9405315679919283</v>
       </c>
       <c r="D2">
-        <v>0.6827356175898305</v>
+        <v>0.5592708532113102</v>
       </c>
       <c r="E2">
-        <v>0.7470683357879488</v>
+        <v>0.4019674992848019</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.4491482029126825</v>
+        <v>0.8513702244247343</v>
       </c>
       <c r="C3">
-        <v>0.620716112768283</v>
+        <v>0.6373252090969121</v>
       </c>
       <c r="D3">
-        <v>0.7044409774657061</v>
+        <v>0.5950718841067367</v>
       </c>
       <c r="E3">
-        <v>0.7622186643604321</v>
+        <v>0.5802797082238891</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.3792809828816487</v>
+        <v>0.9251794361379728</v>
       </c>
       <c r="C4">
-        <v>0.5365522613848597</v>
+        <v>0.6958235642380495</v>
       </c>
       <c r="D4">
-        <v>0.6296424307716176</v>
+        <v>0.5119618922484546</v>
       </c>
       <c r="E4">
-        <v>0.7012780821354155</v>
+        <v>0.4417313729998239</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.4857654653692099</v>
+        <v>0.1210653868799424</v>
       </c>
       <c r="C5">
-        <v>0.6639177403196131</v>
+        <v>0.1664933032999649</v>
       </c>
       <c r="D5">
-        <v>0.7328281215101273</v>
+        <v>0.1826398259491184</v>
       </c>
       <c r="E5">
-        <v>0.7844444256025577</v>
+        <v>0.1967182615288147</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.4764492964914863</v>
+        <v>0.5245149088965858</v>
       </c>
       <c r="C6">
-        <v>0.6526352638223125</v>
+        <v>0.5653574061988069</v>
       </c>
       <c r="D6">
-        <v>0.7222865935179038</v>
+        <v>0.6815597131040694</v>
       </c>
       <c r="E6">
-        <v>0.7763724083021228</v>
+        <v>0.8856190549588139</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.5000459747052058</v>
+        <v>0.950087351939891</v>
       </c>
       <c r="C7">
-        <v>0.6794437767110587</v>
+        <v>0.6454715878755057</v>
       </c>
       <c r="D7">
-        <v>0.7533715401581433</v>
+        <v>0.6506390574093054</v>
       </c>
       <c r="E7">
-        <v>0.7937910582919011</v>
+        <v>0.6284179211477552</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.4343970284190021</v>
+        <v>0.1085662782838867</v>
       </c>
       <c r="C8">
-        <v>0.6051242423863379</v>
+        <v>0.151418881180183</v>
       </c>
       <c r="D8">
-        <v>0.6928378562941038</v>
+        <v>0.1731568647828872</v>
       </c>
       <c r="E8">
-        <v>0.7382069388759523</v>
+        <v>0.1844956910704248</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.503969351370773</v>
+        <v>0.9358606307946299</v>
       </c>
       <c r="C9">
-        <v>0.6862152739235847</v>
+        <v>0.7989462973788461</v>
       </c>
       <c r="D9">
-        <v>0.7605472385025487</v>
+        <v>0.6515692824043876</v>
       </c>
       <c r="E9">
-        <v>0.8008314410081749</v>
+        <v>0.5584931131354064</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.5183759225260688</v>
+        <v>0.1303430787854566</v>
       </c>
       <c r="C10">
-        <v>0.6951162783554444</v>
+        <v>0.17277456629644</v>
       </c>
       <c r="D10">
-        <v>0.7614022543224178</v>
+        <v>0.1914508558556369</v>
       </c>
       <c r="E10">
-        <v>0.7924859041778979</v>
+        <v>0.1969762652002868</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.5135506171930706</v>
+        <v>0.1325291915336956</v>
       </c>
       <c r="C11">
-        <v>0.6880779658990894</v>
+        <v>0.1664704756207474</v>
       </c>
       <c r="D11">
-        <v>0.7534768782313206</v>
+        <v>0.1822927931204808</v>
       </c>
       <c r="E11">
-        <v>0.784691742817359</v>
+        <v>0.2025010949206087</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.4800854062337293</v>
+        <v>0.4465475565104434</v>
       </c>
       <c r="C12">
-        <v>0.6241101731037968</v>
+        <v>0.5340723758841101</v>
       </c>
       <c r="D12">
-        <v>0.6614578653373322</v>
+        <v>0.6687193048806347</v>
       </c>
       <c r="E12">
-        <v>0.6770459255562024</v>
+        <v>0.8872049130589887</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.5160629930030343</v>
+        <v>0.1296773674725573</v>
       </c>
       <c r="C13">
-        <v>0.6912035447731096</v>
+        <v>0.1701424110210731</v>
       </c>
       <c r="D13">
-        <v>0.7559454293592841</v>
+        <v>0.1899555181466919</v>
       </c>
       <c r="E13">
-        <v>0.7864898091764774</v>
+        <v>0.1976307725622943</v>
       </c>
     </row>
   </sheetData>
